--- a/ig/test-tabs-svs/CodeSystem-TRE-R212-Equipement.xlsx
+++ b/ig/test-tabs-svs/CodeSystem-TRE-R212-Equipement.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="602">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260601120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>245</t>
+    <t>256</t>
   </si>
   <si>
     <t>Code</t>
@@ -544,7 +544,7 @@
     <t>054</t>
   </si>
   <si>
-    <t>IRM corps entier</t>
+    <t>Imagerie par Résonance Magnétique (IRM) corps entier</t>
   </si>
   <si>
     <t>055</t>
@@ -742,7 +742,7 @@
     <t>087</t>
   </si>
   <si>
-    <t>IRM à champ ouvert</t>
+    <t>Imagerie par Résonance Magnétique (IRM) à champ ouvert</t>
   </si>
   <si>
     <t>088</t>
@@ -1606,7 +1606,7 @@
     <t>221</t>
   </si>
   <si>
-    <t>IRM obésité – bariatrique</t>
+    <t>Imagerie par Résonance Magnétique (IRM) obésité – bariatrique</t>
   </si>
   <si>
     <t>222</t>
@@ -1751,11 +1751,77 @@
 Caisson hyperbare soumis à autorisation"</t>
   </si>
   <si>
+    <t>245</t>
+  </si>
+  <si>
     <t>Cyclotron à usage médical</t>
   </si>
   <si>
     <t>Code créé spécifiquement pour les besoins de FINESS.
 Cyclotron à usage médical soumis à autorisation dans le cadre d'une activité AMM de médecine nucléaire.</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>Échographe polyvalent</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>Imagerie par Résonance Magnétique (IRM) à champ fermé (ou tunnel)</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>Imagerie par Résonance Magnétique (IRM) pédiatrique (compatible anesthésie)</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>Radiologie numérique standard</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>Scanner base dose (LDCT)</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>Plateau réfraction - Pachymétrie</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Rétinographe</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>Oculomètre certifié (C2)</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>Coordimètre</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>Tests scorés et/ou normés en neurovision</t>
+  </si>
+  <si>
+    <t>Accompagnement à l’essai de fauteuil roulant</t>
   </si>
 </sst>
 </file>
@@ -2199,7 +2265,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D246"/>
+  <dimension ref="A1:D257"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5193,14 +5259,146 @@
         <v>68</v>
       </c>
       <c r="B246" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C246" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="D246" t="s" s="2">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C247" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="D247" s="2"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C248" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="D248" s="2"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C249" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="D249" s="2"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C250" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="D250" s="2"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C251" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="D251" s="2"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C252" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="D252" s="2"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C253" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="D253" s="2"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C254" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="D254" s="2"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C255" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="D255" s="2"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B256" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="C256" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="D256" s="2"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B257" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="C246" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="D246" t="s" s="2">
-        <v>579</v>
-      </c>
+      <c r="C257" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="D257" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
